--- a/template/5.29/量化业务日报-.xlsx
+++ b/template/5.29/量化业务日报-.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="量化一-结算数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,41 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D3"/>
+        <bgColor rgb="00FCE4D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+        <bgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DAEEF3"/>
+        <bgColor rgb="00DAEEF3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -42,12 +67,105 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -122,6 +240,61 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,9 +586,465 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>统计日期</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>（金额单位：元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>一、账户资产及收益情况</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="5" t="n"/>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>账户名称</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>量化一</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>账户编号</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>85001</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>资产单元名称</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>量化一-投机单元</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>权益类一单元</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>单元资产净值</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>5885719.94</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>24038441.14</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>账户资产净值</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>29924161.08</v>
+      </c>
+      <c r="C7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>返息/逆回购</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>8888</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>90943.34</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>盈利/亏损（含逆回购/返息）</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>-114280.06</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>38441.14</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损（含逆回购/返息）</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>-75838.91999999806</v>
+      </c>
+      <c r="C10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>收益率（含逆回购/返息）</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>-0.2528%</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>盈利/亏损（不含逆回购/返息）</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>-123168.0599999996</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>-52502.29</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损（不含逆回购/返息）</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>-166782.3499999996</v>
+      </c>
+      <c r="C13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>收益率（不含逆回购/返息）</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>-0.5559%</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>二、净值列示</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>实收资本</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="C16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>资产净值</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>29924161.08</v>
+      </c>
+      <c r="C17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="C18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>期初单位净值</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>昨日单位净值（含逆回购/返息）</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>0.99668</v>
+      </c>
+      <c r="C20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>单位净值（含逆回购/返息）</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="C21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>日净值增长率（含逆回购/返息）</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>0.07947%</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>昨日单位净值（不含逆回购/返息）</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>0.99668</v>
+      </c>
+      <c r="C23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>单位净值（不含逆回购/返息）</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>0.99444</v>
+      </c>
+      <c r="C24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>日净值增长率（不含逆回购/返息）</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>-0.22469%</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>三、保证金使用情况</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>占用</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>429163.2</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>账户权益</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>5885719.94</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>风险度</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>7.2916%</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>四、交易情况</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="140" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>交易方向及数量</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>今日交易: 2 只股指期货合约, 0 只股指期权合约， 成交合约价值 999.55 万元
+卖出开仓: IM2506(3 手),
+买入开仓: IH2506(6 手),
+卖出平仓: IH2506(2 手)</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>买入股票: 770 只, 卖出股票: 0 只, 股票合计成交金额: 444.54 万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>五、持仓情况</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="140" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>持仓品种及数量</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>当前持有: 2 只股指期货合约, 0 只股指期权合约, 持仓合约价值 682.69 万元, 其中: 
+多仓: IH2506(4 手),
+空仓: IM2506(3 手)</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>股票: 771 只</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>注:
+1、盈利/亏损（不含逆回购）数据暂未包含中金所申报费，盈利/亏损（含逆回购）数据已包含中金所申报费。2、返息: 8888.0元。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>